--- a/tools/importer/reports/import-about-page.report.xlsx
+++ b/tools/importer/reports/import-about-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>about.report.json</t>
   </si>
   <si>
-    <t>["teaser","carousel","columns","columns","columns","columns","columns","columns","columns","fragment","fragment"]</t>
+    <t>["teaser","carousel","columns","columns","columns","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>about</t>
@@ -52,7 +52,7 @@
     <t>about-page</t>
   </si>
   <si>
-    <t>2026-08-19T05:48:08.201Z</t>
+    <t>2026-08-19T08:26:29.394Z</t>
   </si>
   <si>
     <t>About | Hoegemeyer Hybrids</t>

--- a/tools/importer/reports/import-about-page.report.xlsx
+++ b/tools/importer/reports/import-about-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>about.report.json</t>
   </si>
   <si>
-    <t>["teaser","carousel","columns","columns","columns","columns","columns","columns","columns"]</t>
+    <t>["breadcrumb","teaser","carousel","columns","columns","columns","columns","columns","columns","columns"]</t>
   </si>
   <si>
     <t>about</t>
@@ -52,7 +52,7 @@
     <t>about-page</t>
   </si>
   <si>
-    <t>2026-08-19T08:26:29.394Z</t>
+    <t>2026-08-19T08:38:38.836Z</t>
   </si>
   <si>
     <t>About | Hoegemeyer Hybrids</t>
